--- a/Caracterizacion_Haces/data/z4mm-852.xlsx
+++ b/Caracterizacion_Haces/data/z4mm-852.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="138">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,298 +128,316 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-685,2</t>
+    <t>784,3</t>
+  </si>
+  <si>
+    <t>122,5</t>
+  </si>
+  <si>
+    <t>139,4</t>
+  </si>
+  <si>
+    <t>144,4</t>
+  </si>
+  <si>
+    <t>116,4</t>
+  </si>
+  <si>
+    <t>107,5</t>
+  </si>
+  <si>
+    <t>118,2</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>783,7</t>
+  </si>
+  <si>
+    <t>122,8</t>
+  </si>
+  <si>
+    <t>139,7</t>
+  </si>
+  <si>
+    <t>145,0</t>
+  </si>
+  <si>
+    <t>116,5</t>
+  </si>
+  <si>
+    <t>107,2</t>
+  </si>
+  <si>
+    <t>118,6</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>785,4</t>
+  </si>
+  <si>
+    <t>122,9</t>
+  </si>
+  <si>
+    <t>139,8</t>
+  </si>
+  <si>
+    <t>145,4</t>
+  </si>
+  <si>
+    <t>116,2</t>
+  </si>
+  <si>
+    <t>117,9</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>786,4</t>
   </si>
   <si>
     <t>121,3</t>
   </si>
   <si>
-    <t>146,7</t>
-  </si>
-  <si>
-    <t>148,7</t>
-  </si>
-  <si>
-    <t>118,7</t>
-  </si>
-  <si>
-    <t>110,3</t>
-  </si>
-  <si>
-    <t>125,2</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>-686,3</t>
-  </si>
-  <si>
-    <t>121,6</t>
-  </si>
-  <si>
-    <t>147,9</t>
-  </si>
-  <si>
-    <t>150,3</t>
-  </si>
-  <si>
-    <t>110,4</t>
-  </si>
-  <si>
-    <t>125,3</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>122,1</t>
-  </si>
-  <si>
-    <t>150,5</t>
-  </si>
-  <si>
-    <t>118,9</t>
-  </si>
-  <si>
-    <t>110,0</t>
-  </si>
-  <si>
-    <t>124,7</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>122,5</t>
-  </si>
-  <si>
-    <t>119,3</t>
-  </si>
-  <si>
-    <t>110,1</t>
-  </si>
-  <si>
-    <t>124,5</t>
+    <t>143,7</t>
+  </si>
+  <si>
+    <t>116,1</t>
+  </si>
+  <si>
+    <t>107,4</t>
   </si>
   <si>
     <t>0,8</t>
   </si>
   <si>
-    <t>-685,7</t>
-  </si>
-  <si>
-    <t>120,8</t>
-  </si>
-  <si>
-    <t>147,6</t>
-  </si>
-  <si>
-    <t>149,9</t>
+    <t>784,8</t>
+  </si>
+  <si>
+    <t>140,0</t>
+  </si>
+  <si>
+    <t>145,6</t>
+  </si>
+  <si>
+    <t>107,0</t>
+  </si>
+  <si>
+    <t>118,4</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>786,2</t>
+  </si>
+  <si>
+    <t>122,6</t>
+  </si>
+  <si>
+    <t>145,3</t>
+  </si>
+  <si>
+    <t>116,0</t>
+  </si>
+  <si>
+    <t>106,9</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>121,8</t>
+  </si>
+  <si>
+    <t>144,5</t>
+  </si>
+  <si>
+    <t>106,6</t>
+  </si>
+  <si>
+    <t>118,1</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>785,6</t>
+  </si>
+  <si>
+    <t>120,7</t>
+  </si>
+  <si>
+    <t>144,3</t>
+  </si>
+  <si>
+    <t>115,5</t>
+  </si>
+  <si>
+    <t>118,8</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>122,3</t>
+  </si>
+  <si>
+    <t>144,9</t>
+  </si>
+  <si>
+    <t>106,8</t>
+  </si>
+  <si>
+    <t>118,3</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>121,7</t>
+  </si>
+  <si>
+    <t>139,5</t>
+  </si>
+  <si>
+    <t>144,8</t>
+  </si>
+  <si>
+    <t>115,4</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>121,9</t>
+  </si>
+  <si>
+    <t>140,7</t>
+  </si>
+  <si>
+    <t>145,8</t>
+  </si>
+  <si>
+    <t>115,8</t>
+  </si>
+  <si>
+    <t>107,3</t>
+  </si>
+  <si>
+    <t>117,8</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>139,0</t>
+  </si>
+  <si>
+    <t>144,0</t>
+  </si>
+  <si>
+    <t>107,6</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>785,1</t>
+  </si>
+  <si>
+    <t>123,5</t>
+  </si>
+  <si>
+    <t>116,6</t>
   </si>
   <si>
     <t>118,0</t>
   </si>
   <si>
-    <t>124,8</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>-686,0</t>
-  </si>
-  <si>
-    <t>121,8</t>
-  </si>
-  <si>
-    <t>146,6</t>
-  </si>
-  <si>
-    <t>119,2</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>-687,6</t>
-  </si>
-  <si>
-    <t>146,9</t>
-  </si>
-  <si>
-    <t>149,1</t>
-  </si>
-  <si>
-    <t>118,6</t>
-  </si>
-  <si>
-    <t>125,1</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>-686,5</t>
-  </si>
-  <si>
-    <t>147,5</t>
-  </si>
-  <si>
-    <t>149,6</t>
-  </si>
-  <si>
-    <t>119,1</t>
-  </si>
-  <si>
-    <t>109,9</t>
-  </si>
-  <si>
-    <t>125,4</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>-684,4</t>
-  </si>
-  <si>
-    <t>121,9</t>
-  </si>
-  <si>
-    <t>150,2</t>
-  </si>
-  <si>
-    <t>110,2</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>122,3</t>
-  </si>
-  <si>
-    <t>147,1</t>
-  </si>
-  <si>
-    <t>149,5</t>
-  </si>
-  <si>
-    <t>119,4</t>
-  </si>
-  <si>
-    <t>124,9</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>-686,8</t>
-  </si>
-  <si>
-    <t>147,4</t>
-  </si>
-  <si>
-    <t>124,4</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>119,0</t>
-  </si>
-  <si>
-    <t>109,7</t>
-  </si>
-  <si>
-    <t>124,6</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>-684,7</t>
-  </si>
-  <si>
     <t>2,6</t>
   </si>
   <si>
-    <t>147,3</t>
-  </si>
-  <si>
-    <t>149,4</t>
-  </si>
-  <si>
-    <t>118,2</t>
-  </si>
-  <si>
-    <t>109,8</t>
+    <t>785,9</t>
+  </si>
+  <si>
+    <t>122,4</t>
+  </si>
+  <si>
+    <t>139,9</t>
+  </si>
+  <si>
+    <t>145,1</t>
+  </si>
+  <si>
+    <t>106,7</t>
+  </si>
+  <si>
+    <t>117,6</t>
   </si>
   <si>
     <t>2,8</t>
   </si>
   <si>
-    <t>149,8</t>
+    <t>120,1</t>
+  </si>
+  <si>
+    <t>141,6</t>
+  </si>
+  <si>
+    <t>146,0</t>
+  </si>
+  <si>
+    <t>114,8</t>
   </si>
   <si>
     <t>3,0</t>
   </si>
   <si>
-    <t>-684,9</t>
-  </si>
-  <si>
-    <t>147,8</t>
+    <t>140,1</t>
   </si>
   <si>
     <t>3,2</t>
   </si>
   <si>
-    <t>150,0</t>
-  </si>
-  <si>
-    <t>110,6</t>
+    <t>123,1</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>121,0</t>
-  </si>
-  <si>
-    <t>147,2</t>
-  </si>
-  <si>
-    <t>149,3</t>
-  </si>
-  <si>
-    <t>118,4</t>
+    <t>140,4</t>
+  </si>
+  <si>
+    <t>145,7</t>
+  </si>
+  <si>
+    <t>115,9</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>121,5</t>
-  </si>
-  <si>
-    <t>147,7</t>
-  </si>
-  <si>
-    <t>150,1</t>
+    <t>123,0</t>
+  </si>
+  <si>
+    <t>116,7</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>122,7</t>
+  </si>
+  <si>
+    <t>140,2</t>
   </si>
   <si>
     <t>118,5</t>
-  </si>
-  <si>
-    <t>3,8</t>
-  </si>
-  <si>
-    <t>121,2</t>
-  </si>
-  <si>
-    <t>148,6</t>
-  </si>
-  <si>
-    <t>118,8</t>
   </si>
 </sst>
 </file>
@@ -760,7 +778,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -768,7 +786,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59229166666666666</v>
+        <v>0.76855324074074083</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -909,7 +927,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2774</v>
+        <v>1082</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -938,7 +956,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2772</v>
+        <v>1082</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -950,245 +968,245 @@
         <v>45</v>
       </c>
       <c r="G24" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="H24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C25">
-        <v>2774</v>
+        <v>1084</v>
       </c>
       <c r="D25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E25" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G25" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H25" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I25" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C26">
-        <v>2778</v>
+        <v>1084</v>
       </c>
       <c r="D26" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="H26" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="I26" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C27">
-        <v>2774</v>
+        <v>1083</v>
       </c>
       <c r="D27" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="H27" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="I27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C28">
-        <v>2773</v>
+        <v>1085</v>
       </c>
       <c r="D28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="G28" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H28" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C29">
-        <v>2774</v>
+        <v>1081</v>
       </c>
       <c r="D29" t="s">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="E29" t="s">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="H29" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="I29" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C30">
-        <v>2774</v>
+        <v>1084</v>
       </c>
       <c r="D30" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="F30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H30" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="I30" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C31">
-        <v>2776</v>
+        <v>1082</v>
       </c>
       <c r="D31" t="s">
         <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="F31" t="s">
         <v>87</v>
       </c>
       <c r="G31" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="H31" t="s">
         <v>88</v>
       </c>
       <c r="I31" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C32">
+        <v>1083</v>
+      </c>
+      <c r="D32" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" t="s">
+        <v>93</v>
+      </c>
+      <c r="G32" t="s">
+        <v>94</v>
+      </c>
+      <c r="H32" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" t="s">
         <v>89</v>
-      </c>
-      <c r="B32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32">
-        <v>2775</v>
-      </c>
-      <c r="D32" t="s">
-        <v>90</v>
-      </c>
-      <c r="E32" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" t="s">
-        <v>92</v>
-      </c>
-      <c r="G32" t="s">
-        <v>93</v>
-      </c>
-      <c r="H32" t="s">
-        <v>52</v>
-      </c>
-      <c r="I32" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
@@ -1196,289 +1214,289 @@
         <v>95</v>
       </c>
       <c r="B33" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33">
+        <v>1084</v>
+      </c>
+      <c r="D33" t="s">
         <v>96</v>
-      </c>
-      <c r="C33">
-        <v>2772</v>
-      </c>
-      <c r="D33" t="s">
-        <v>68</v>
       </c>
       <c r="E33" t="s">
         <v>97</v>
       </c>
       <c r="F33" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="G33" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C34">
-        <v>2776</v>
+        <v>1083</v>
       </c>
       <c r="D34" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="F34" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="H34" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I34" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C35">
-        <v>2774</v>
+        <v>1084</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E35" t="s">
-        <v>97</v>
+        <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="G35" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="H35" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="I35" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="C36">
-        <v>2773</v>
+        <v>1084</v>
       </c>
       <c r="D36" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="E36" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="F36" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>108</v>
+        <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="I36" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="B37" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C37">
-        <v>2774</v>
+        <v>1085</v>
       </c>
       <c r="D37" t="s">
-        <v>49</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="G37" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H37" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>50</v>
       </c>
       <c r="C38">
-        <v>2773</v>
+        <v>1084</v>
       </c>
       <c r="D38" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G38" t="s">
-        <v>100</v>
+        <v>54</v>
       </c>
       <c r="H38" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B39" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C39">
-        <v>2773</v>
+        <v>1083</v>
       </c>
       <c r="D39" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>106</v>
+        <v>44</v>
       </c>
       <c r="F39" t="s">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="G39" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="I39" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B40" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C40">
-        <v>2776</v>
+        <v>1083</v>
       </c>
       <c r="D40" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E40" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="F40" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H40" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B41" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
       <c r="C41">
-        <v>2776</v>
+        <v>1084</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="E41" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
       <c r="F41" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="G41" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="H41" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="I41" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="C42">
-        <v>2773</v>
+        <v>1084</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
       <c r="F42" t="s">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="G42" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="H42" t="s">
-        <v>52</v>
+        <v>105</v>
       </c>
       <c r="I42" t="s">
-        <v>53</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
